--- a/results/link-prediction-gcn/Link/0shot/MUTAG/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/MUTAG/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6565±0.0126</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6272±0.0326</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6619±0.0000</t>
+          <t>0.6657±0.0032</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.7083±0.0150</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6619±0.0000</t>
+          <t>0.6988±0.0259</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6498±0.0384</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7415±0.0123</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7415±0.0123</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7415±0.0123</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.7174±0.0000</t>
+          <t>0.6390±0.0030</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.7482±0.0000</t>
+          <t>0.7036±0.0309</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6637±0.0000</t>
+          <t>0.7369±0.0067</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.5313±0.1385</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6671±0.0057</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.6530±0.0000</t>
+          <t>0.6555±0.0065</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.6554±0.0000</t>
+          <t>0.6607±0.0102</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.6583±0.0000</t>
+          <t>0.6738±0.0135</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6623±0.0015</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6579±0.0236</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6915±0.0215</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6915±0.0215</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6915±0.0215</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6851±0.0326</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6333±0.0000</t>
+          <t>0.6200±0.0350</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6673±0.0132</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.6315±0.0000</t>
+          <t>0.7024±0.0097</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5170±0.0000</t>
+          <t>0.5690±0.0317</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5411±0.0000</t>
+          <t>0.6911±0.0395</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.7284±0.0157</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5635±0.0000</t>
+          <t>0.7014±0.0183</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5689±0.0000</t>
+          <t>0.7090±0.0108</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5546±0.0000</t>
+          <t>0.7058±0.0010</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5546±0.0000</t>
+          <t>0.7058±0.0010</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5546±0.0000</t>
+          <t>0.7058±0.0010</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5564±0.0000</t>
+          <t>0.6428±0.0158</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5331±0.0000</t>
+          <t>0.5262±0.0116</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5653±0.0000</t>
+          <t>0.7190±0.0030</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.7250±0.0000</t>
+          <t>0.7238±0.0059</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5796±0.0000</t>
+          <t>0.6792±0.0208</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.7370±0.0000</t>
+          <t>0.6831±0.0325</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.7308±0.0073</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.7138±0.0000</t>
+          <t>0.7053±0.0107</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.7196±0.0000</t>
+          <t>0.7058±0.0145</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.7429±0.0000</t>
+          <t>0.6820±0.0073</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.7429±0.0000</t>
+          <t>0.6820±0.0073</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.7429±0.0000</t>
+          <t>0.6820±0.0073</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.7281±0.0000</t>
+          <t>0.7082±0.0173</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.6500±0.0000</t>
+          <t>0.6506±0.0080</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.7500±0.0000</t>
+          <t>0.7004±0.0110</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6651±0.0006</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.6196±0.0000</t>
+          <t>0.6665±0.0316</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.6530±0.0000</t>
+          <t>0.6381±0.0146</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.6488±0.0097</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.7268±0.0000</t>
+          <t>0.6762±0.0290</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.7163±0.0216</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.7268±0.0000</t>
+          <t>0.6450±0.0174</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.7268±0.0000</t>
+          <t>0.6450±0.0174</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.7268±0.0000</t>
+          <t>0.6450±0.0174</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6918±0.0420</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7250±0.0000</t>
+          <t>0.6973±0.0347</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.7321±0.0000</t>
+          <t>0.7274±0.0135</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6329±0.0460</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.6696±0.0000</t>
+          <t>0.6798±0.0280</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.6547±0.0000</t>
+          <t>0.6564±0.0138</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.7321±0.0000</t>
+          <t>0.6567±0.0165</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.6820±0.0302</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6988±0.0452</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7153±0.0291</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7169±0.0222</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7080±0.0332</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6357±0.0000</t>
+          <t>0.6708±0.0304</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.7393±0.0000</t>
+          <t>0.6650±0.0446</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.7357±0.0000</t>
+          <t>0.7298±0.0194</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.3345±0.0000</t>
+          <t>0.3353±0.0006</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.6929±0.0236</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5943±0.0000</t>
+          <t>0.6349±0.0459</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6562±0.0433</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6804±0.0227</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.6814±0.0051</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6977±0.0000</t>
+          <t>0.6867±0.0089</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6625±0.0282</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6625±0.0282</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6625±0.0282</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.6982±0.0000</t>
+          <t>0.6671±0.0326</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6429±0.0000</t>
+          <t>0.6131±0.0298</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.6964±0.0000</t>
+          <t>0.7014±0.0084</t>
         </is>
       </c>
     </row>
@@ -1360,452 +1360,452 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7813±0.0252</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7408±0.0464</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7961±0.0000</t>
+          <t>0.7986±0.0018</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.8008±0.0105</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7961±0.0000</t>
+          <t>0.8050±0.0077</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7437±0.0383</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8205±0.0083</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8205±0.0083</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8205±0.0083</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8128±0.0000</t>
+          <t>0.7283±0.0034</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8287±0.0000</t>
+          <t>0.7892±0.0297</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8208±0.0035</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>0.4831±0.3416</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.7962±0.0019</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.7802±0.0145</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.7889±0.0080</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.7901±0.0035</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.7968±0.0011</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7696±0.0312</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8017±0.0036</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8017±0.0036</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8017±0.0036</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7767±0.0281</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7122±0.0367</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.7909±0.0030</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.7983±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.7900±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.7914±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.7940±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.7983±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7248±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.7957±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.7916±0.0069</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6871±0.0180</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.7768±0.0334</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.8131±0.0084</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.7865±0.0175</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7936±0.0098</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7938±0.0031</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7938±0.0031</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7938±0.0031</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.7363±0.0138</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6068±0.0054</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.8033±0.0025</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.7311±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6778±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6915±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.7551±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6504±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6620±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6438±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6438±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6438±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6477±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6015±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6543±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.8081±0.0038</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.7832±0.0200</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.7701±0.0322</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.8163±0.0028</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.8020±0.0058</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7913±0.0078</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7816±0.0097</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7816±0.0097</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7816±0.0097</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7983±0.0088</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7445±0.0067</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7955±0.0065</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.8145±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.7320±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.8227±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.7987±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.8091±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.8111±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.8257±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.8257±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.8257±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.8160±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7387±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.8297±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.7989±0.0004</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.7608±0.0232</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7331±0.0099</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.7380±0.0087</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.7671±0.0235</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.8010±0.0173</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7384±0.0122</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7384±0.0122</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7384±0.0122</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7774±0.0372</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7828±0.0314</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.8087±0.0123</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.7991±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.7625±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.7887±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.8114±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.8099±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.7991±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.8099±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.8099±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.8099±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.7991±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.8089±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.8144±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.7712±0.0395</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.7778±0.0197</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.7451±0.0124</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.7487±0.0177</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.7706±0.0273</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.7841±0.0389</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.7985±0.0247</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.8042±0.0232</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.7943±0.0271</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.7571±0.0305</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.7549±0.0380</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.8106±0.0167</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.7983±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.8004±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.7758±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.8157±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.8114±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.7991±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.8109±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.8109±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.8109±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.7753±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.8202±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.8164±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.7605±0.0000</t>
+          <t>0.7826±0.0204</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.7420±0.0000</t>
+          <t>0.7652±0.0241</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7679±0.0000</t>
+          <t>0.7506±0.0415</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7956±0.0000</t>
+          <t>0.8014±0.0044</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7593±0.0000</t>
+          <t>0.7819±0.0083</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.8000±0.0000</t>
+          <t>0.7825±0.0092</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.7891±0.0000</t>
+          <t>0.7616±0.0226</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.7891±0.0000</t>
+          <t>0.7616±0.0226</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.7891±0.0000</t>
+          <t>0.7616±0.0226</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.8033±0.0000</t>
+          <t>0.7662±0.0280</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7297±0.0000</t>
+          <t>0.7065±0.0302</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.7962±0.0000</t>
+          <t>0.7945±0.0069</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5971±0.0000</t>
+          <t>0.7232±0.0756</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5757±0.0000</t>
+          <t>0.5555±0.0065</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3877±0.0000</t>
+          <t>0.4689±0.0613</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6330±0.0000</t>
+          <t>0.6449±0.0196</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5386±0.0000</t>
+          <t>0.6235±0.0076</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5668±0.0000</t>
+          <t>0.5678±0.0082</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5793±0.0000</t>
+          <t>0.6162±0.0143</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.6371±0.0058</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.6372±0.0058</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.6372±0.0059</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5810±0.0000</t>
+          <t>0.6314±0.0059</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6399±0.0000</t>
+          <t>0.6509±0.0235</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.6004±0.0000</t>
+          <t>0.6388±0.0165</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5719±0.0000</t>
+          <t>0.6143±0.0503</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.6421±0.0096</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4388±0.0000</t>
+          <t>0.5147±0.0243</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6972±0.0000</t>
+          <t>0.6522±0.0525</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5557±0.0000</t>
+          <t>0.5701±0.0709</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6266±0.0000</t>
+          <t>0.6039±0.0204</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.6542±0.0000</t>
+          <t>0.6369±0.0185</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6292±0.0000</t>
+          <t>0.6272±0.0181</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6292±0.0000</t>
+          <t>0.6272±0.0181</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6292±0.0000</t>
+          <t>0.6272±0.0181</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.6429±0.0000</t>
+          <t>0.6504±0.0219</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6287±0.0000</t>
+          <t>0.6328±0.0254</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6454±0.0000</t>
+          <t>0.6377±0.0207</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7167±0.0000</t>
+          <t>0.6477±0.1656</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.5158±0.0000</t>
+          <t>0.6052±0.0183</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.3964±0.0000</t>
+          <t>0.4847±0.0539</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.3857±0.0000</t>
+          <t>0.5730±0.0221</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.4964±0.0000</t>
+          <t>0.6230±0.0055</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5367±0.0000</t>
+          <t>0.6121±0.0177</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5353±0.0000</t>
+          <t>0.6237±0.0260</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5201±0.0000</t>
+          <t>0.5950±0.0042</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5201±0.0000</t>
+          <t>0.5950±0.0042</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5201±0.0000</t>
+          <t>0.5950±0.0042</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5360±0.0000</t>
+          <t>0.6144±0.0277</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.5115±0.0000</t>
+          <t>0.5765±0.0263</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5313±0.0000</t>
+          <t>0.6260±0.0193</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.8005±0.0000</t>
+          <t>0.5372±0.0486</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.6087±0.0000</t>
+          <t>0.6540±0.0010</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4396±0.0000</t>
+          <t>0.5993±0.0230</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6538±0.0000</t>
+          <t>0.6514±0.0102</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5013±0.0000</t>
+          <t>0.6509±0.0055</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6207±0.0000</t>
+          <t>0.6005±0.0234</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6150±0.0000</t>
+          <t>0.6258±0.0358</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6605±0.0000</t>
+          <t>0.6108±0.0085</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6605±0.0000</t>
+          <t>0.6108±0.0085</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6605±0.0000</t>
+          <t>0.6108±0.0085</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.5789±0.0000</t>
+          <t>0.6331±0.0245</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.6682±0.0000</t>
+          <t>0.6621±0.0053</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6740±0.0000</t>
+          <t>0.6327±0.0226</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7968±0.0000</t>
+          <t>0.7562±0.0403</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5974±0.0000</t>
+          <t>0.5676±0.0356</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2697±0.0000</t>
+          <t>0.5765±0.0461</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4901±0.0000</t>
+          <t>0.6065±0.0182</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6254±0.0000</t>
+          <t>0.6466±0.0156</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6323±0.0000</t>
+          <t>0.6304±0.0236</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5916±0.0000</t>
+          <t>0.6296±0.0088</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6327±0.0000</t>
+          <t>0.6331±0.0285</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6327±0.0000</t>
+          <t>0.6331±0.0285</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6327±0.0000</t>
+          <t>0.6331±0.0285</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5881±0.0000</t>
+          <t>0.6357±0.0097</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.6534±0.0000</t>
+          <t>0.6636±0.0104</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6512±0.0000</t>
+          <t>0.6618±0.0066</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.5915±0.0000</t>
+          <t>0.7004±0.0494</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5733±0.0249</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.2346±0.0000</t>
+          <t>0.5216±0.0799</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.4472±0.0000</t>
+          <t>0.6167±0.0265</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6374±0.0000</t>
+          <t>0.6638±0.0075</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6239±0.0000</t>
+          <t>0.6359±0.0163</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.6280±0.0074</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6263±0.0000</t>
+          <t>0.6418±0.0104</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6263±0.0000</t>
+          <t>0.6231±0.0324</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6263±0.0000</t>
+          <t>0.6302±0.0226</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5934±0.0000</t>
+          <t>0.6422±0.0135</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6490±0.0000</t>
+          <t>0.6547±0.0036</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6444±0.0000</t>
+          <t>0.6604±0.0086</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5171±0.0000</t>
+          <t>0.6882±0.0178</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5928±0.0000</t>
+          <t>0.6479±0.0144</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4530±0.0000</t>
+          <t>0.5073±0.0693</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5883±0.0000</t>
+          <t>0.6110±0.0152</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5055±0.0000</t>
+          <t>0.5396±0.0560</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5777±0.0000</t>
+          <t>0.5990±0.0113</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5350±0.0000</t>
+          <t>0.5784±0.0084</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5727±0.0000</t>
+          <t>0.6001±0.0086</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5727±0.0000</t>
+          <t>0.6001±0.0086</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5727±0.0000</t>
+          <t>0.6001±0.0086</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5276±0.0000</t>
+          <t>0.5754±0.0201</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.6377±0.0000</t>
+          <t>0.6233±0.0161</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6011±0.0000</t>
+          <t>0.6176±0.0032</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7207±0.0000</t>
+          <t>0.8056±0.0602</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6745±0.0000</t>
+          <t>0.6610±0.0123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6130±0.0000</t>
+          <t>0.6302±0.0175</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7347±0.0000</t>
+          <t>0.7421±0.0176</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6503±0.0000</t>
+          <t>0.7322±0.0028</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6622±0.0000</t>
+          <t>0.6786±0.0176</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6791±0.0000</t>
+          <t>0.7284±0.0234</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6520±0.0000</t>
+          <t>0.7356±0.0022</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6520±0.0000</t>
+          <t>0.7355±0.0023</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6520±0.0000</t>
+          <t>0.7357±0.0023</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.7474±0.0050</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7401±0.0000</t>
+          <t>0.7394±0.0136</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6945±0.0000</t>
+          <t>0.7242±0.0231</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6837±0.0000</t>
+          <t>0.7346±0.0387</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.7064±0.0109</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6374±0.0000</t>
+          <t>0.6718±0.0115</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.8161±0.0000</t>
+          <t>0.7584±0.0540</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6946±0.0000</t>
+          <t>0.7022±0.0377</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7219±0.0000</t>
+          <t>0.6916±0.0134</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7179±0.0000</t>
+          <t>0.7313±0.0135</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.7388±0.0147</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.7388±0.0147</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.7388±0.0147</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7138±0.0000</t>
+          <t>0.7393±0.0363</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7444±0.0250</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7175±0.0000</t>
+          <t>0.7442±0.0128</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8266±0.0000</t>
+          <t>0.7691±0.1070</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6959±0.0117</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6176±0.0000</t>
+          <t>0.6345±0.0106</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5870±0.0000</t>
+          <t>0.6633±0.0112</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6294±0.0000</t>
+          <t>0.7277±0.0141</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6614±0.0000</t>
+          <t>0.6871±0.0100</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6663±0.0000</t>
+          <t>0.7076±0.0200</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6574±0.0000</t>
+          <t>0.6757±0.0052</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6573±0.0000</t>
+          <t>0.6757±0.0052</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6573±0.0000</t>
+          <t>0.6758±0.0053</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6716±0.0000</t>
+          <t>0.7234±0.0159</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7010±0.0000</t>
+          <t>0.7191±0.0173</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6585±0.0000</t>
+          <t>0.6990±0.0134</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.8764±0.0000</t>
+          <t>0.6771±0.0335</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6948±0.0000</t>
+          <t>0.7509±0.0026</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6394±0.0000</t>
+          <t>0.7155±0.0172</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7479±0.0000</t>
+          <t>0.7520±0.0085</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.7480±0.0023</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7290±0.0000</t>
+          <t>0.7185±0.0151</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.7304±0.0268</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7521±0.0000</t>
+          <t>0.7288±0.0046</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7521±0.0000</t>
+          <t>0.7288±0.0046</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7521±0.0000</t>
+          <t>0.7289±0.0046</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6613±0.0000</t>
+          <t>0.7423±0.0177</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7609±0.0000</t>
+          <t>0.7602±0.0071</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7599±0.0000</t>
+          <t>0.7415±0.0159</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.8605±0.0000</t>
+          <t>0.8266±0.0318</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6852±0.0000</t>
+          <t>0.6643±0.0223</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5228±0.0000</t>
+          <t>0.6700±0.0288</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6158±0.0000</t>
+          <t>0.7139±0.0153</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7049±0.0000</t>
+          <t>0.7513±0.0108</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7071±0.0000</t>
+          <t>0.7438±0.0181</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6808±0.0000</t>
+          <t>0.7160±0.0235</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7065±0.0000</t>
+          <t>0.7423±0.0195</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7066±0.0000</t>
+          <t>0.7424±0.0195</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7065±0.0000</t>
+          <t>0.7423±0.0195</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.7291±0.0241</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7510±0.0000</t>
+          <t>0.7591±0.0076</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7499±0.0221</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7242±0.0000</t>
+          <t>0.7928±0.0430</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6779±0.0000</t>
+          <t>0.6708±0.0162</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5097±0.0000</t>
+          <t>0.6365±0.0478</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5901±0.0000</t>
+          <t>0.7128±0.0231</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7187±0.0000</t>
+          <t>0.7740±0.0118</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.7388±0.0180</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6833±0.0000</t>
+          <t>0.7161±0.0203</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7025±0.0000</t>
+          <t>0.7353±0.0208</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7025±0.0000</t>
+          <t>0.7117±0.0377</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7025±0.0000</t>
+          <t>0.7254±0.0252</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6815±0.0000</t>
+          <t>0.7472±0.0243</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7499±0.0000</t>
+          <t>0.7524±0.0153</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7088±0.0000</t>
+          <t>0.7501±0.0216</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6457±0.0000</t>
+          <t>0.7914±0.0323</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7079±0.0000</t>
+          <t>0.7534±0.0158</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6478±0.0000</t>
+          <t>0.6721±0.0363</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7047±0.0000</t>
+          <t>0.7190±0.0086</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6703±0.0000</t>
+          <t>0.6848±0.0290</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7007±0.0000</t>
+          <t>0.7120±0.0046</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.7153±0.0057</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6995±0.0000</t>
+          <t>0.7116±0.0040</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6995±0.0000</t>
+          <t>0.7116±0.0040</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6995±0.0000</t>
+          <t>0.7116±0.0040</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.6627±0.0000</t>
+          <t>0.7018±0.0075</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7642±0.0000</t>
+          <t>0.7469±0.0073</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7224±0.0035</t>
         </is>
       </c>
     </row>
